--- a/output/stock_quant_scores/PLTR_income_df.xlsx
+++ b/output/stock_quant_scores/PLTR_income_df.xlsx
@@ -1251,7 +1251,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>-484854000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>14139000</v>
@@ -1264,7 +1266,9 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.27</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>-5483000</v>
@@ -1273,7 +1277,9 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-520379000</v>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1296,9 +1302,13 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>1202485000</v>
+      </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1541889000</v>
+      </c>
       <c r="AW6" t="inlineStr"/>
     </row>
   </sheetData>
